--- a/public/templates/users-import-template-student.xlsx
+++ b/public/templates/users-import-template-student.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="6">
   <si>
     <t>Name</t>
   </si>
@@ -23,16 +23,10 @@
     <t>Email</t>
   </si>
   <si>
-    <t>Photo Filename</t>
-  </si>
-  <si>
     <t>Alex Putri</t>
   </si>
   <si>
     <t>alex.putri@example.com</t>
-  </si>
-  <si>
-    <t>alex-putri.jpg</t>
   </si>
   <si>
     <t>Budi Santoso</t>
@@ -388,42 +382,35 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="15.282" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="29.421" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="17.567" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
